--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008436103227840842</v>
       </c>
       <c r="C2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>23429565</v>
+        <v>4391981</v>
       </c>
       <c r="L2" t="n">
-        <v>13848224</v>
+        <v>2345022</v>
       </c>
       <c r="M2" t="n">
-        <v>3552037</v>
+        <v>537455</v>
       </c>
       <c r="N2" t="n">
-        <v>210761</v>
+        <v>23888</v>
       </c>
       <c r="O2" t="n">
-        <v>2094352</v>
+        <v>328828</v>
       </c>
       <c r="P2" t="n">
-        <v>835362</v>
+        <v>142229</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999885559082031</v>
+        <v>0.9999889731407166</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9187706708908081</v>
+        <v>0.8487072587013245</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8359636664390564</v>
+        <v>0.7103025913238525</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7981232404708862</v>
+        <v>0.6413903832435608</v>
       </c>
       <c r="U2" t="n">
-        <v>0.54758620262146</v>
+        <v>0.2250061184167862</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8377307653427124</v>
+        <v>0.704556941986084</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8832762241363525</v>
+        <v>0.779905378818512</v>
       </c>
       <c r="X2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565883278846741</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112817645072937</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580537438392639</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622784733772278</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019806981086731</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002021821095387664</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>23429565</v>
+        <v>4391981</v>
       </c>
       <c r="E3" t="n">
-        <v>1855020</v>
+        <v>646823</v>
       </c>
       <c r="F3" t="n">
-        <v>27663</v>
+        <v>10878</v>
       </c>
       <c r="G3" t="n">
-        <v>4071</v>
+        <v>1406</v>
       </c>
       <c r="H3" t="n">
-        <v>1510</v>
+        <v>761</v>
       </c>
       <c r="I3" t="n">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>50347736</v>
+        <v>10069550</v>
       </c>
       <c r="K3" t="n">
-        <v>54690602</v>
+        <v>10581190</v>
       </c>
       <c r="L3" t="n">
-        <v>62963098</v>
+        <v>12169481</v>
       </c>
       <c r="M3" t="n">
-        <v>76510982</v>
+        <v>15180384</v>
       </c>
       <c r="N3" t="n">
-        <v>81459290</v>
+        <v>16244303</v>
       </c>
       <c r="O3" t="n">
-        <v>79127470</v>
+        <v>15768406</v>
       </c>
       <c r="P3" t="n">
-        <v>81003023</v>
+        <v>16182469</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9254124760627747</v>
+        <v>0.8693748712539673</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8444273471832275</v>
+        <v>0.7127509713172913</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7605149745941162</v>
+        <v>0.5747456550598145</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4719445705413818</v>
+        <v>0.2671467959880829</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8223296999931335</v>
+        <v>0.6451326608657837</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8642405867576599</v>
+        <v>0.7354402542114258</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>995349</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>42884</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>34102</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50348100</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55661737</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>64227600</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76746838</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81482703</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79283607</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>81047145</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576305150985718</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099767208099365</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575676679611206</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618276834487915</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016205072402954</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03192545378405855</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1960532</v>
+        <v>741732</v>
       </c>
       <c r="E4" t="n">
-        <v>13848224</v>
+        <v>2345022</v>
       </c>
       <c r="F4" t="n">
-        <v>533637</v>
+        <v>176217</v>
       </c>
       <c r="G4" t="n">
-        <v>20042</v>
+        <v>10284</v>
       </c>
       <c r="H4" t="n">
-        <v>34121</v>
+        <v>15191</v>
       </c>
       <c r="I4" t="n">
-        <v>2982</v>
+        <v>1652</v>
       </c>
       <c r="J4" t="n">
-        <v>364</v>
+        <v>70</v>
       </c>
       <c r="K4" t="n">
-        <v>2071428</v>
+        <v>782926</v>
       </c>
       <c r="L4" t="n">
-        <v>2717357</v>
+        <v>956419</v>
       </c>
       <c r="M4" t="n">
-        <v>898450</v>
+        <v>300498</v>
       </c>
       <c r="N4" t="n">
-        <v>174130</v>
+        <v>82278</v>
       </c>
       <c r="O4" t="n">
-        <v>405678</v>
+        <v>137888</v>
       </c>
       <c r="P4" t="n">
-        <v>110392</v>
+        <v>40138</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999942779541016</v>
+        <v>0.9999944567680359</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9220795631408691</v>
+        <v>0.858916699886322</v>
       </c>
       <c r="S4" t="n">
-        <v>0.84017413854599</v>
+        <v>0.7115247249603271</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7788653969764709</v>
+        <v>0.6062420010566711</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5069593787193298</v>
+        <v>0.2442722916603088</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8299587965011597</v>
+        <v>0.6735365986824036</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8736547231674194</v>
+        <v>0.7570204734802246</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1027338</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>415378</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27557</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1100293</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1452855</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>662594</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>150717</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249541</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571090936660767</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106287360191345</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578105568885803</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620529890060425</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018005132675171</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>69272</v>
+        <v>26987</v>
       </c>
       <c r="E5" t="n">
-        <v>749333</v>
+        <v>265786</v>
       </c>
       <c r="F5" t="n">
-        <v>3552037</v>
+        <v>537455</v>
       </c>
       <c r="G5" t="n">
-        <v>69548</v>
+        <v>28828</v>
       </c>
       <c r="H5" t="n">
-        <v>215038</v>
+        <v>68592</v>
       </c>
       <c r="I5" t="n">
-        <v>15325</v>
+        <v>7466</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1888405</v>
+        <v>659903</v>
       </c>
       <c r="L5" t="n">
-        <v>2551321</v>
+        <v>945078</v>
       </c>
       <c r="M5" t="n">
-        <v>1118531</v>
+        <v>397663</v>
       </c>
       <c r="N5" t="n">
-        <v>235819</v>
+        <v>65531</v>
       </c>
       <c r="O5" t="n">
-        <v>452500</v>
+        <v>180878</v>
       </c>
       <c r="P5" t="n">
-        <v>131223</v>
+        <v>51164</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999955892562866</v>
+        <v>0.9999957084655762</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9517564177513123</v>
+        <v>0.9121083617210388</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9358104467391968</v>
+        <v>0.8841680884361267</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9754266738891602</v>
+        <v>0.957470715045929</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9950054883956909</v>
+        <v>0.9909960627555847</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9895446300506592</v>
+        <v>0.9805819988250732</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9970563650131226</v>
+        <v>0.9944382309913635</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40265</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>426214</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49808</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145788</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1072710</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1476341</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>665240</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>151021</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250558</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735257625579834</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643129110336304</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838227033615112</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963238835334778</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939071536064148</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383641242981</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>41144</v>
+        <v>13846</v>
       </c>
       <c r="E6" t="n">
-        <v>68797</v>
+        <v>19529</v>
       </c>
       <c r="F6" t="n">
-        <v>84167</v>
+        <v>21204</v>
       </c>
       <c r="G6" t="n">
-        <v>210761</v>
+        <v>23888</v>
       </c>
       <c r="H6" t="n">
-        <v>37920</v>
+        <v>9594</v>
       </c>
       <c r="I6" t="n">
-        <v>3733</v>
+        <v>1343</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32411</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26831</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54451</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34923</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>397</v>
+        <v>327</v>
       </c>
       <c r="E7" t="n">
-        <v>42105</v>
+        <v>23130</v>
       </c>
       <c r="F7" t="n">
-        <v>244846</v>
+        <v>88081</v>
       </c>
       <c r="G7" t="n">
-        <v>76818</v>
+        <v>39684</v>
       </c>
       <c r="H7" t="n">
-        <v>2094352</v>
+        <v>328828</v>
       </c>
       <c r="I7" t="n">
-        <v>88218</v>
+        <v>29645</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4056</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148230</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37923</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="E8" t="n">
-        <v>2102</v>
+        <v>1151</v>
       </c>
       <c r="F8" t="n">
-        <v>8137</v>
+        <v>4118</v>
       </c>
       <c r="G8" t="n">
-        <v>3651</v>
+        <v>2076</v>
       </c>
       <c r="H8" t="n">
-        <v>117089</v>
+        <v>43750</v>
       </c>
       <c r="I8" t="n">
-        <v>835362</v>
+        <v>142229</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
